--- a/uploads/menu_data_updated.xlsx
+++ b/uploads/menu_data_updated.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4fdae77fc648ca8d/Desktop/SAAS_MENU/saas-menu-app-backend/uploads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="80" documentId="8_{A2AF0A05-CFD6-44AF-B283-622CE488AF25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00FF7370-1CC8-41A4-8894-619FAE936CDD}"/>
+  <xr:revisionPtr revIDLastSave="84" documentId="8_{A2AF0A05-CFD6-44AF-B283-622CE488AF25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2515D6C6-13CA-45AB-848B-C643F099D990}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="110">
   <si>
     <t>type</t>
   </si>
@@ -361,9 +361,6 @@
   </si>
   <si>
     <t>Item Desc</t>
-  </si>
-  <si>
-    <t>Serves 5</t>
   </si>
 </sst>
 </file>
@@ -975,13 +972,13 @@
         <v>103</v>
       </c>
       <c r="F14">
-        <v>250</v>
+        <v>150</v>
       </c>
       <c r="G14" t="s">
         <v>34</v>
       </c>
       <c r="H14" t="s">
-        <v>110</v>
+        <v>36</v>
       </c>
       <c r="I14">
         <v>100</v>
